--- a/docs/superpowers/verification/admin-session-grants/review-artifacts/registrations_Session_Grant_Review_Event_A.xlsx
+++ b/docs/superpowers/verification/admin-session-grants/review-artifacts/registrations_Session_Grant_Review_Event_A.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>30/9/2569 22:42:43</v>
+        <v>1/10/2569 07:09:38</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>30/9/2569 22:42:42</v>
+        <v>1/10/2569 07:09:37</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>30/9/2569 22:42:41</v>
+        <v>1/10/2569 07:09:36</v>
       </c>
     </row>
     <row r="5">
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>30/9/2569 22:42:40</v>
+        <v>1/10/2569 07:09:35</v>
       </c>
     </row>
     <row r="6">
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>30/9/2569 22:42:39</v>
+        <v>1/10/2569 07:09:34</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>30/9/2569 22:42:38</v>
+        <v>1/10/2569 07:09:33</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>30/9/2569 22:42:37</v>
+        <v>1/10/2569 07:09:32</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>30/9/2569 22:42:36</v>
+        <v>1/10/2569 07:09:31</v>
       </c>
     </row>
     <row r="10">
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>30/9/2569 22:42:35</v>
+        <v>1/10/2569 07:09:30</v>
       </c>
     </row>
     <row r="11">
@@ -781,7 +781,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>30/9/2569 22:42:34</v>
+        <v>1/10/2569 07:09:29</v>
       </c>
     </row>
     <row r="12">
@@ -816,7 +816,7 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>30/9/2569 22:42:33</v>
+        <v>1/10/2569 07:09:28</v>
       </c>
     </row>
     <row r="13">
@@ -851,7 +851,7 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>30/9/2569 22:42:32</v>
+        <v>1/10/2569 07:09:27</v>
       </c>
     </row>
     <row r="14">
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>30/9/2569 22:42:31</v>
+        <v>1/10/2569 07:09:26</v>
       </c>
     </row>
     <row r="15">
@@ -921,7 +921,7 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>30/9/2569 22:42:30</v>
+        <v>1/10/2569 07:09:25</v>
       </c>
     </row>
     <row r="16">
@@ -956,7 +956,7 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>30/9/2569 22:42:29</v>
+        <v>1/10/2569 07:09:24</v>
       </c>
     </row>
     <row r="17">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>30/9/2569 22:42:28</v>
+        <v>1/10/2569 07:09:23</v>
       </c>
     </row>
     <row r="18">
@@ -1026,7 +1026,7 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>30/9/2569 22:42:27</v>
+        <v>1/10/2569 07:09:22</v>
       </c>
     </row>
     <row r="19">
@@ -1061,7 +1061,7 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>30/9/2569 22:42:26</v>
+        <v>1/10/2569 07:09:21</v>
       </c>
     </row>
     <row r="20">
@@ -1096,7 +1096,7 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>30/9/2569 22:42:25</v>
+        <v>1/10/2569 07:09:20</v>
       </c>
     </row>
     <row r="21">
@@ -1131,7 +1131,7 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>30/9/2569 22:42:24</v>
+        <v>1/10/2569 07:09:19</v>
       </c>
     </row>
     <row r="22">
@@ -1166,7 +1166,7 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>30/9/2569 22:42:23</v>
+        <v>1/10/2569 07:09:18</v>
       </c>
     </row>
     <row r="23">
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>30/9/2569 22:42:22</v>
+        <v>1/10/2569 07:09:17</v>
       </c>
     </row>
     <row r="24">
@@ -1236,7 +1236,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>30/9/2569 22:42:21</v>
+        <v>1/10/2569 07:09:16</v>
       </c>
     </row>
     <row r="25">
@@ -1271,7 +1271,7 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>30/9/2569 22:42:20</v>
+        <v>1/10/2569 07:09:15</v>
       </c>
     </row>
     <row r="26">
@@ -1306,7 +1306,7 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>30/9/2569 22:42:19</v>
+        <v>1/10/2569 07:09:14</v>
       </c>
     </row>
     <row r="27">
@@ -1341,7 +1341,7 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>30/9/2569 22:42:18</v>
+        <v>1/10/2569 07:09:13</v>
       </c>
     </row>
     <row r="28">
@@ -1376,7 +1376,7 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>30/9/2569 22:42:17</v>
+        <v>1/10/2569 07:09:12</v>
       </c>
     </row>
     <row r="29">
@@ -1411,7 +1411,7 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>30/9/2569 22:42:16</v>
+        <v>1/10/2569 07:09:11</v>
       </c>
     </row>
     <row r="30">
@@ -1446,7 +1446,7 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>30/9/2569 22:42:15</v>
+        <v>1/10/2569 07:09:10</v>
       </c>
     </row>
     <row r="31">
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>30/9/2569 22:42:14</v>
+        <v>1/10/2569 07:09:09</v>
       </c>
     </row>
     <row r="32">
@@ -1516,7 +1516,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>30/9/2569 22:42:13</v>
+        <v>1/10/2569 07:09:08</v>
       </c>
     </row>
     <row r="33">
@@ -1551,7 +1551,7 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>30/9/2569 22:42:12</v>
+        <v>1/10/2569 07:09:07</v>
       </c>
     </row>
     <row r="34">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>30/9/2569 22:42:11</v>
+        <v>1/10/2569 07:09:06</v>
       </c>
     </row>
     <row r="35">
@@ -1621,7 +1621,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>30/9/2569 22:42:10</v>
+        <v>1/10/2569 07:09:05</v>
       </c>
     </row>
     <row r="36">
@@ -1656,7 +1656,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>30/9/2569 22:42:09</v>
+        <v>1/10/2569 07:09:04</v>
       </c>
     </row>
     <row r="37">
@@ -1691,7 +1691,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>30/9/2569 22:42:08</v>
+        <v>1/10/2569 07:09:03</v>
       </c>
     </row>
     <row r="38">
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>30/9/2569 22:42:07</v>
+        <v>1/10/2569 07:09:02</v>
       </c>
     </row>
     <row r="39">
@@ -1761,7 +1761,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>30/9/2569 22:42:06</v>
+        <v>1/10/2569 07:09:01</v>
       </c>
     </row>
     <row r="40">
@@ -1796,7 +1796,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>30/9/2569 22:42:05</v>
+        <v>1/10/2569 07:09:00</v>
       </c>
     </row>
     <row r="41">
@@ -1831,7 +1831,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>30/9/2569 22:42:04</v>
+        <v>1/10/2569 07:08:59</v>
       </c>
     </row>
     <row r="42">
@@ -1866,7 +1866,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>30/9/2569 22:42:03</v>
+        <v>1/10/2569 07:08:58</v>
       </c>
     </row>
     <row r="43">
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>30/9/2569 22:42:02</v>
+        <v>1/10/2569 07:08:57</v>
       </c>
     </row>
     <row r="44">
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>30/9/2569 22:42:01</v>
+        <v>1/10/2569 07:08:56</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>30/9/2569 22:42:00</v>
+        <v>1/10/2569 07:08:55</v>
       </c>
     </row>
     <row r="46">
@@ -2006,7 +2006,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>30/9/2569 22:41:59</v>
+        <v>1/10/2569 07:08:54</v>
       </c>
     </row>
     <row r="47">
@@ -2041,7 +2041,7 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>30/9/2569 22:41:58</v>
+        <v>1/10/2569 07:08:53</v>
       </c>
     </row>
     <row r="48">
@@ -2076,7 +2076,7 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>30/9/2569 22:41:57</v>
+        <v>1/10/2569 07:08:52</v>
       </c>
     </row>
     <row r="49">
@@ -2111,7 +2111,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>30/9/2569 22:41:56</v>
+        <v>1/10/2569 07:08:51</v>
       </c>
     </row>
     <row r="50">
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>30/9/2569 22:41:55</v>
+        <v>1/10/2569 07:08:50</v>
       </c>
     </row>
     <row r="51">
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>30/9/2569 22:41:54</v>
+        <v>1/10/2569 07:08:49</v>
       </c>
     </row>
     <row r="52">
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>30/9/2569 22:41:53</v>
+        <v>1/10/2569 07:08:48</v>
       </c>
     </row>
     <row r="53">
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>30/9/2569 22:41:52</v>
+        <v>1/10/2569 07:08:47</v>
       </c>
     </row>
     <row r="54">
@@ -2286,7 +2286,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>30/9/2569 22:41:51</v>
+        <v>1/10/2569 07:08:46</v>
       </c>
     </row>
     <row r="55">
@@ -2321,7 +2321,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>30/9/2569 22:41:50</v>
+        <v>1/10/2569 07:08:45</v>
       </c>
     </row>
     <row r="56">
@@ -2356,7 +2356,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>30/9/2569 22:41:49</v>
+        <v>1/10/2569 07:08:44</v>
       </c>
     </row>
     <row r="57">
@@ -2391,7 +2391,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>30/9/2569 22:41:48</v>
+        <v>1/10/2569 07:08:43</v>
       </c>
     </row>
     <row r="58">
@@ -2426,7 +2426,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>30/9/2569 22:41:47</v>
+        <v>1/10/2569 07:08:42</v>
       </c>
     </row>
     <row r="59">
@@ -2461,7 +2461,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>30/9/2569 22:41:46</v>
+        <v>1/10/2569 07:08:41</v>
       </c>
     </row>
     <row r="60">
@@ -2496,7 +2496,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>30/9/2569 22:41:45</v>
+        <v>1/10/2569 07:08:40</v>
       </c>
     </row>
     <row r="61">
@@ -2531,7 +2531,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>30/9/2569 22:41:44</v>
+        <v>1/10/2569 07:08:39</v>
       </c>
     </row>
     <row r="62">
@@ -2566,7 +2566,7 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>30/9/2569 22:41:43</v>
+        <v>1/10/2569 07:08:38</v>
       </c>
     </row>
     <row r="63">
@@ -2601,7 +2601,7 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>30/9/2569 22:41:42</v>
+        <v>1/10/2569 07:08:37</v>
       </c>
     </row>
     <row r="64">
@@ -2636,7 +2636,7 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>30/9/2569 22:41:41</v>
+        <v>1/10/2569 07:08:36</v>
       </c>
     </row>
     <row r="65">
@@ -2671,7 +2671,7 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>30/9/2569 22:41:40</v>
+        <v>1/10/2569 07:08:35</v>
       </c>
     </row>
     <row r="66">
@@ -2706,7 +2706,7 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>30/9/2569 22:41:39</v>
+        <v>1/10/2569 07:08:34</v>
       </c>
     </row>
     <row r="67">
@@ -2741,7 +2741,7 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>30/9/2569 22:41:38</v>
+        <v>1/10/2569 07:08:33</v>
       </c>
     </row>
     <row r="68">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>30/9/2569 22:41:37</v>
+        <v>1/10/2569 07:08:32</v>
       </c>
     </row>
     <row r="69">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>30/9/2569 22:41:36</v>
+        <v>1/10/2569 07:08:31</v>
       </c>
     </row>
     <row r="70">
@@ -2846,7 +2846,7 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>30/9/2569 22:41:35</v>
+        <v>1/10/2569 07:08:30</v>
       </c>
     </row>
     <row r="71">
@@ -2881,7 +2881,7 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>30/9/2569 22:41:34</v>
+        <v>1/10/2569 07:08:29</v>
       </c>
     </row>
     <row r="72">
@@ -2916,7 +2916,7 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>30/9/2569 22:41:33</v>
+        <v>1/10/2569 07:08:28</v>
       </c>
     </row>
     <row r="73">
@@ -2951,7 +2951,7 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>30/9/2569 22:41:32</v>
+        <v>1/10/2569 07:08:27</v>
       </c>
     </row>
     <row r="74">
@@ -2986,7 +2986,7 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>30/9/2569 22:41:31</v>
+        <v>1/10/2569 07:08:26</v>
       </c>
     </row>
     <row r="75">
@@ -3021,7 +3021,7 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>30/9/2569 22:41:30</v>
+        <v>1/10/2569 07:08:25</v>
       </c>
     </row>
     <row r="76">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>30/9/2569 22:41:29</v>
+        <v>1/10/2569 07:08:24</v>
       </c>
     </row>
     <row r="77">
@@ -3091,7 +3091,7 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>30/9/2569 22:41:28</v>
+        <v>1/10/2569 07:08:23</v>
       </c>
     </row>
     <row r="78">
@@ -3126,7 +3126,7 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>30/9/2569 22:41:27</v>
+        <v>1/10/2569 07:08:22</v>
       </c>
     </row>
     <row r="79">
@@ -3161,7 +3161,7 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>30/9/2569 22:41:26</v>
+        <v>1/10/2569 07:08:21</v>
       </c>
     </row>
     <row r="80">
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>30/9/2569 22:41:25</v>
+        <v>1/10/2569 07:08:20</v>
       </c>
     </row>
     <row r="81">
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>30/9/2569 22:41:24</v>
+        <v>1/10/2569 07:08:19</v>
       </c>
     </row>
     <row r="82">
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>30/9/2569 22:41:23</v>
+        <v>1/10/2569 07:08:18</v>
       </c>
     </row>
     <row r="83">
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>30/9/2569 22:41:22</v>
+        <v>1/10/2569 07:08:17</v>
       </c>
     </row>
     <row r="84">
@@ -3336,7 +3336,7 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>30/9/2569 22:41:21</v>
+        <v>1/10/2569 07:08:16</v>
       </c>
     </row>
     <row r="85">
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>30/9/2569 22:41:20</v>
+        <v>1/10/2569 07:08:15</v>
       </c>
     </row>
     <row r="86">
@@ -3406,7 +3406,7 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>30/9/2569 22:41:19</v>
+        <v>1/10/2569 07:08:14</v>
       </c>
     </row>
     <row r="87">
@@ -3441,7 +3441,7 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>30/9/2569 22:41:18</v>
+        <v>1/10/2569 07:08:13</v>
       </c>
     </row>
     <row r="88">
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>30/9/2569 22:41:17</v>
+        <v>1/10/2569 07:08:12</v>
       </c>
     </row>
     <row r="89">
@@ -3511,7 +3511,7 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>30/9/2569 22:41:16</v>
+        <v>1/10/2569 07:08:11</v>
       </c>
     </row>
     <row r="90">
@@ -3546,7 +3546,7 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>30/9/2569 22:41:15</v>
+        <v>1/10/2569 07:08:10</v>
       </c>
     </row>
     <row r="91">
@@ -3581,7 +3581,7 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>30/9/2569 22:41:14</v>
+        <v>1/10/2569 07:08:09</v>
       </c>
     </row>
     <row r="92">
@@ -3616,7 +3616,7 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>30/9/2569 22:41:13</v>
+        <v>1/10/2569 07:08:08</v>
       </c>
     </row>
     <row r="93">
@@ -3651,7 +3651,7 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>30/9/2569 22:41:12</v>
+        <v>1/10/2569 07:08:07</v>
       </c>
     </row>
     <row r="94">
@@ -3686,7 +3686,7 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>30/9/2569 22:41:11</v>
+        <v>1/10/2569 07:08:06</v>
       </c>
     </row>
     <row r="95">
@@ -3721,7 +3721,7 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>30/9/2569 22:41:10</v>
+        <v>1/10/2569 07:08:05</v>
       </c>
     </row>
     <row r="96">
@@ -3756,7 +3756,7 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>30/9/2569 22:41:09</v>
+        <v>1/10/2569 07:08:04</v>
       </c>
     </row>
     <row r="97">
@@ -3791,7 +3791,7 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>30/9/2569 22:41:08</v>
+        <v>1/10/2569 07:08:03</v>
       </c>
     </row>
     <row r="98">
@@ -3826,7 +3826,7 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>30/9/2569 22:41:07</v>
+        <v>1/10/2569 07:08:02</v>
       </c>
     </row>
     <row r="99">
@@ -3861,7 +3861,7 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>30/9/2569 22:41:06</v>
+        <v>1/10/2569 07:08:01</v>
       </c>
     </row>
     <row r="100">
@@ -3896,7 +3896,7 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>30/9/2569 22:41:05</v>
+        <v>1/10/2569 07:08:00</v>
       </c>
     </row>
     <row r="101">
@@ -3931,7 +3931,7 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>30/9/2569 22:41:04</v>
+        <v>1/10/2569 07:07:59</v>
       </c>
     </row>
     <row r="102">
@@ -3966,7 +3966,7 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>30/9/2569 22:41:03</v>
+        <v>1/10/2569 07:07:58</v>
       </c>
     </row>
     <row r="103">
@@ -4001,7 +4001,7 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>30/9/2569 22:41:02</v>
+        <v>1/10/2569 07:07:57</v>
       </c>
     </row>
     <row r="104">
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>30/9/2569 22:41:01</v>
+        <v>1/10/2569 07:07:56</v>
       </c>
     </row>
     <row r="105">
@@ -4071,7 +4071,7 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>30/9/2569 22:41:00</v>
+        <v>1/10/2569 07:07:55</v>
       </c>
     </row>
     <row r="106">
@@ -4106,7 +4106,7 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>30/9/2569 22:40:59</v>
+        <v>1/10/2569 07:07:54</v>
       </c>
     </row>
   </sheetData>
